--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-18).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-18).xlsx
@@ -915,30 +915,30 @@
   </si>
   <si>
     <t>215
-164</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 1.700.458,04</t>
-  </si>
-  <si>
-    <t>R$ 9.343,18
-R$ 9.742,06</t>
-  </si>
-  <si>
-    <t>0.2%
-4.3%</t>
-  </si>
-  <si>
-    <t>100.8</t>
-  </si>
-  <si>
-    <t>(5.0%)</t>
-  </si>
-  <si>
-    <t>31.0%</t>
+172</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>R$ 1.754.124,24</t>
+  </si>
+  <si>
+    <t>R$ 9.232,23
+R$ 9.600,95</t>
+  </si>
+  <si>
+    <t>(0.1%)
+3.7%</t>
+  </si>
+  <si>
+    <t>99.5</t>
+  </si>
+  <si>
+    <t>(5.4%)</t>
+  </si>
+  <si>
+    <t>30.7%</t>
   </si>
   <si>
     <t>(9.5%)</t>
@@ -950,19 +950,16 @@
     <t>0.7%</t>
   </si>
   <si>
-    <t>30.7</t>
-  </si>
-  <si>
-    <t>57.3%</t>
-  </si>
-  <si>
-    <t>16.8%</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>7.8</t>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>57.5%</t>
+  </si>
+  <si>
+    <t>16.9%</t>
+  </si>
+  <si>
+    <t>7.7</t>
   </si>
   <si>
     <t>15.9</t>
@@ -971,10 +968,10 @@
     <t>22.5</t>
   </si>
   <si>
-    <t>59.8%</t>
-  </si>
-  <si>
-    <t>-R$ 33.134,70</t>
+    <t>59.7%</t>
+  </si>
+  <si>
+    <t>-R$ 33.711,80</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>16314.32</v>
+      </c>
+      <c r="P6" s="5">
+        <v>16314.32</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>0.21989996627656661</v>
+      </c>
+      <c r="R6" s="7">
+        <v>165</v>
+      </c>
+      <c r="S6" s="6">
+        <v>0.15384615384615374</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.25555706888181673</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.0030427379136856456</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.025792064885327735</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0034576985127176612</v>
+      </c>
+      <c r="X6" s="8">
+        <v>30.243905223880599</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.92537313432835822</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.26119402985074625</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>13.502710843373492</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>2.5021141791044776</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>17.217039</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>24.17549776119403</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.55970149253731338</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7852,7 +7885,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7888,25 +7921,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>633.14999999999998</v>
+      </c>
+      <c r="P51" s="5">
+        <v>633.14999999999998</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.67569685608039576</v>
+      </c>
+      <c r="R51" s="7">
+        <v>7</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.63157894736842102</v>
+      </c>
+      <c r="T51" s="6">
+        <v>-0.0081497275527126281</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.34105662165363659</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.028862828713574984</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.1733167495854063</v>
+      </c>
+      <c r="X51" s="8">
+        <v>63.995825000000004</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>10.352385714285715</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>43.383324999999999</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>62.899999999999999</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.25</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8777,7 +8844,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>17.210232999999999</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -9473,7 +9542,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>44</v>
@@ -9507,25 +9576,61 @@
       <c t="s" r="N64" s="4">
         <v>52</v>
       </c>
-      <c r="O64" s="5"/>
-      <c r="P64" s="5"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
-      <c r="X64" s="8"/>
-      <c r="Y64" s="6"/>
-      <c r="Z64" s="6"/>
-      <c r="AA64" s="8"/>
-      <c r="AB64" s="8"/>
-      <c r="AC64" s="8"/>
-      <c r="AD64" s="8"/>
-      <c r="AE64" s="6"/>
+      <c r="O64" s="5">
+        <v>7896.8599999999997</v>
+      </c>
+      <c r="P64" s="5">
+        <v>7896.8599999999997</v>
+      </c>
+      <c r="Q64" s="6">
+        <v>-0.097355227934133315</v>
+      </c>
+      <c r="R64" s="7">
+        <v>87</v>
+      </c>
+      <c r="S64" s="6">
+        <v>-0.20183486238532111</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0.27434900707369764</v>
+      </c>
+      <c r="U64" s="6">
+        <v>-0.029580656108883784</v>
+      </c>
+      <c r="V64" s="6">
+        <v>0.021840136459301548</v>
+      </c>
+      <c r="W64" s="6">
+        <v>0.00019609059803516843</v>
+      </c>
+      <c r="X64" s="8">
+        <v>26.975609756097562</v>
+      </c>
+      <c r="Y64" s="6">
+        <v>0.56097560975609762</v>
+      </c>
+      <c r="Z64" s="6">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AA64" s="8">
+        <v>4.2874034883720933</v>
+      </c>
+      <c r="AB64" s="8">
+        <v>11.709999999999999</v>
+      </c>
+      <c r="AC64" s="8">
+        <v>17.036829000000001</v>
+      </c>
+      <c r="AD64" s="8">
+        <v>23.664634146341463</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>0.73170731707317072</v>
+      </c>
       <c r="AF64" s="9"/>
-      <c r="AG64" s="5"/>
+      <c r="AG64" s="5">
+        <v>-377.60000000000002</v>
+      </c>
       <c r="AH64" s="10">
         <v>1</v>
       </c>
@@ -14189,7 +14294,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14225,25 +14330,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>8426.1700000000001</v>
+      </c>
+      <c r="P102" s="5">
+        <v>8426.1700000000001</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.2344849139516989</v>
+      </c>
+      <c r="R102" s="7">
+        <v>89</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.25210084033613445</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.34613709431449879</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.016864601592419808</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.0033341363869943286</v>
+      </c>
+      <c r="X102" s="8">
+        <v>47.838281250000001</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.078125</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.59375</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>15.327592222222224</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>8.84375</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>25.504103000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>32.261457812499998</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.046875</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -20340,7 +20481,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20376,25 +20517,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>5877.96</v>
+      </c>
+      <c r="P151" s="5">
+        <v>5877.96</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.28540566694911851</v>
+      </c>
+      <c r="R151" s="7">
+        <v>64</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.29670329670329665</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.29280005307963985</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.0055959890846484159</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.02464247800257232</v>
+      </c>
+      <c r="W151" s="6">
+        <v>-0.0012270413544835284</v>
+      </c>
+      <c r="X151" s="8">
+        <v>26.790833333333335</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.016666666666666666</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>7.7458328124999998</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>3.0866071428571429</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>10.93994</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>17.540278333333333</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21090,7 +21267,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21126,25 +21303,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>4256.1000000000004</v>
+      </c>
+      <c r="P157" s="5">
+        <v>4256.1000000000004</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.21281876761683516</v>
+      </c>
+      <c r="R157" s="7">
+        <v>43</v>
+      </c>
+      <c r="S157" s="6">
+        <v>-0.27118644067796616</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.26905885669979557</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.0080633913676840304</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.053622330302389512</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.027983834966283684</v>
+      </c>
+      <c r="X157" s="8">
+        <v>26.865316216216218</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>5.8565883720930234</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>2.9148648648648647</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>8.6873860000000001</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>15.634235135135134</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.72972972972972971</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21185,7 +21398,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21221,25 +21434,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>4253.7299999999996</v>
+      </c>
+      <c r="P158" s="5">
+        <v>4253.7299999999996</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.35280173692626737</v>
+      </c>
+      <c r="R158" s="7">
+        <v>41</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.43055555555555558</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.24971084201395016</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.014429101047786297</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.036826032681905062</v>
+      </c>
+      <c r="W158" s="6">
+        <v>0.0056769000383193107</v>
+      </c>
+      <c r="X158" s="8">
+        <v>27.330951428571428</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.0101634146341461</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>4.2557142857142853</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>10.581638999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>17.379048571428573</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.62857142857142856</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22060,7 +22309,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22096,25 +22345,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>6007.9099999999999</v>
+      </c>
+      <c r="P165" s="5">
+        <v>6007.9099999999999</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.11857063596385053</v>
+      </c>
+      <c r="R165" s="7">
+        <v>63</v>
+      </c>
+      <c r="S165" s="6">
+        <v>-0.059701492537313383</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.28894345953917422</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0014387199541937214</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.019829358295979798</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.0044469707435697272</v>
+      </c>
+      <c r="X165" s="8">
+        <v>20.3729175</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>5.6912573770491806</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>2.0358974358974362</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>7.7055550000000004</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>14.333332500000001</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.97499999999999998</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-147.59999999999999</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
@@ -28460,26 +28745,26 @@
         <v>315</v>
       </c>
       <c t="s" r="AB217" s="14">
+        <v>315</v>
+      </c>
+      <c t="s" r="AC217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AC217" s="14">
+      <c t="s" r="AD217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AD217" s="14">
+      <c t="s" r="AE217" s="14">
         <v>318</v>
-      </c>
-      <c t="s" r="AE217" s="14">
-        <v>319</v>
       </c>
       <c r="AF217" s="14"/>
       <c t="s" r="AG217" s="14">
+        <v>319</v>
+      </c>
+      <c t="s" r="AH217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AH217" s="14">
+      <c t="s" r="AI217" s="14">
         <v>321</v>
-      </c>
-      <c t="s" r="AI217" s="14">
-        <v>322</v>
       </c>
       <c r="AJ217" s="15"/>
       <c t="s" r="AK217" s="15">
@@ -28489,10 +28774,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM217" s="14">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN217" s="14">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AO217" s="15"/>
       <c r="AP217" s="15"/>
